--- a/output/pdf_financials_xlsx/MOLT.xlsx
+++ b/output/pdf_financials_xlsx/MOLT.xlsx
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.012852</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003515</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.940593</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.012852</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003515</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.940593</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.024914</v>
+        <v>0.012062</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.003515</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.277647</v>
+        <v>0.337054</v>
       </c>
     </row>
     <row r="49">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
